--- a/CE国試data/CE_questions_2014.xlsx
+++ b/CE国試data/CE_questions_2014.xlsx
@@ -2307,7 +2307,7 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
@@ -4288,7 +4288,7 @@
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
@@ -4485,7 +4485,7 @@
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
@@ -5689,7 +5689,7 @@
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T58" t="inlineStr">
@@ -6398,7 +6398,7 @@
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T60" t="inlineStr">
@@ -7475,7 +7475,7 @@
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T71" t="inlineStr">
@@ -9539,7 +9539,7 @@
       </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T92" t="inlineStr">
@@ -13570,7 +13570,7 @@
       </c>
       <c r="S133" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T133" t="inlineStr">
@@ -14561,7 +14561,7 @@
       </c>
       <c r="S143" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T143" t="inlineStr">
@@ -14952,7 +14952,7 @@
       </c>
       <c r="S147" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T147" t="inlineStr">
@@ -15154,7 +15154,7 @@
       </c>
       <c r="S149" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T149" t="inlineStr">
